--- a/media/ViewUploadedBills/836086478_May_2025.xlsx
+++ b/media/ViewUploadedBills/836086478_May_2025.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="161">
   <si>
     <t>Company</t>
   </si>
@@ -88,7 +88,7 @@
     <t>2025</t>
   </si>
   <si>
-    <t>$1268.73</t>
+    <t>$1293.5900000000001</t>
   </si>
   <si>
     <t>Wireless Number</t>
@@ -262,64 +262,67 @@
     <t>Active</t>
   </si>
   <si>
-    <t>Talk Used Plan minutes (unlimited) 821, Text Used 7 of 36, Text Used Plan messages (unlimited) 88, Data Used $0.14 UNLIMITED QCI8 - 75 5G DATA ALL 15.45, Data Used APPLEIPHONE 16 PLUS 280000075570543, Data Used $53.34 Established on Oct 29, 2024,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 1,000, Text Used Plan messages (unlimited) 10, Data Used UNLIMITED QCI8 - 75 DATA ALL 3.79,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 1, Talk Used of 36, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 0.30, Data Used APPLEIPHONE 14 128GB 280000070791972, Data Used Government fees &amp; taxes Established on Feb 26, 2024,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 85, Text Used Plan messages (unlimited) 13,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 470, Text Used Plan messages (unlimited) 208, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 60.48,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 1,227, Text Used Plan messages (unlimited) 80, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 0.38,</t>
-  </si>
-  <si>
-    <t>Talk Used $0.00 Plan minutes (unlimited) 38, Talk Used Call over Wi-Fi 23, Text Used $0.26 Plan messages (unlimited) 20, Data Used Government fees &amp; taxes Bus. Unlim Plus with Private WiFi 44.47,</t>
-  </si>
-  <si>
-    <t>Talk Used $0.00 Plan minutes (unlimited) 256, Text Used $0.35 Plan messages (unlimited) 39, Data Used Bus. Unlim Plus with Private WiFi 45.54,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 7,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 1,561, Text Used $0.02 Plan messages (unlimited) 2, Data Used Bus. Unlim Plus with Private WiFi 0.07,</t>
-  </si>
-  <si>
-    <t>Talk Used $0.00 Plan minutes (unlimited) 1,204, Text Used $0.20 Plan messages (unlimited) 66, Data Used $0.02 Bus. Unlim Plus with Private WiFi 10.04,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 3,395, Text Used $0.18 Plan messages (unlimited) 92, Data Used $0.44 Bus. Unlim Plus with Private WiFi 26.80,</t>
-  </si>
-  <si>
-    <t>Talk Used $0.00 Plan minutes (unlimited) 9, Text Used Company fees &amp; surcharges Plan messages (unlimited) 144, Data Used $1.50 Bus. Unlim Plus with Private WiFi 0.16,</t>
-  </si>
-  <si>
-    <t>Talk Used Plan minutes (unlimited) 251, Data Used $0.40 Bus. Unlim Plus with Private WiFi 0.14,</t>
+    <t>Talk Used Plan minutes (unlimited) 426, Text Used 8 of 36, Text Used Plan messages (unlimited) 88, Data Used $0.14 UNLIMITED QCI8 - 75 5G DATA ALL 12.76, Data Used APPLEIPHONE 16 PLUS 280000075570543, Data Used $53.34 Established on Oct 29, 2024,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 847, Text Used Plan messages (unlimited) 9, Data Used UNLIMITED QCI8 - 75 DATA ALL 0.41,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 9, Talk Used of 36, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 0.26, Data Used APPLEIPHONE 14 128GB 280000070791972, Data Used Government fees &amp; taxes Established on Feb 26, 2024,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 83, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 0.81,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 502, Text Used Plan messages (unlimited) 367, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 57.36,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 933, Text Used Plan messages (unlimited) 54, Data Used UNLIMITED QCI8 - 75 5G DATA ALL 0.20,</t>
+  </si>
+  <si>
+    <t>Talk Used $0.00 Plan minutes (unlimited) 27, Talk Used Call over Wi-Fi 51, Text Used $0.26 Plan messages (unlimited) 24, Data Used Government fees &amp; taxes Bus. Unlim Plus with Private WiFi 38.07,</t>
+  </si>
+  <si>
+    <t>Talk Used $0.00 Plan minutes (unlimited) 234, Text Used $0.35 Plan messages (unlimited) 17, Data Used Bus. Unlim Plus with Private WiFi 42.39,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 1, Text Used $0.18 Plan messages (unlimited) 1, Data Used $0.44 Bus. Unlim Plus with Private WiFi 0.06,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 1,503, Text Used $0.02 Plan messages (unlimited) 13, Data Used Bus. Unlim Plus with Private WiFi 0.12,</t>
+  </si>
+  <si>
+    <t>Talk Used $0.00 Plan minutes (unlimited) 857,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 2,401, Text Used $0.18 Plan messages (unlimited) 120, Data Used $0.44 Bus. Unlim Plus with Private WiFi 47.21,</t>
+  </si>
+  <si>
+    <t>Talk Used $0.00 Plan minutes (unlimited) 4, Text Used Company fees &amp; surcharges Plan messages (unlimited) 185, Data Used $1.50 Bus. Unlim Plus with Private WiFi 0.68,</t>
+  </si>
+  <si>
+    <t>Talk Used Plan minutes (unlimited) 283, Data Used $0.40 Bus. Unlim Plus with Private WiFi 0.12,</t>
   </si>
   <si>
     <t>Data Used $0.00 Bus. Unlim Plus with Private WiFi 0.00,</t>
   </si>
   <si>
+    <t>Data Used $0.26 Hotspot Wireless Internet Unlim 0.02,</t>
+  </si>
+  <si>
+    <t>Data Used $0.26 Hotspot Wireless Internet Unlim 0.00,</t>
+  </si>
+  <si>
     <t>Data Used $0.26 Hotspot Wireless Internet Unlim 0.01,</t>
   </si>
   <si>
-    <t>Data Used $0.26 Hotspot Wireless Internet Unlim 0.00,</t>
-  </si>
-  <si>
-    <t>Talk Used Company fees &amp; surcharges Daytime minutes (unlimited) 1,137, Talk Used $2.95 Night &amp; Weekend minutes 4, Text Used Government fees &amp; taxes Unlimited Domestic Messaging 102,</t>
-  </si>
-  <si>
-    <t>Talk Used $1.34 Daytime minutes (unlimited) 1,103, Talk Used $0.02 Night &amp; Weekend minutes 236, Text Used Government fees &amp; taxes Unlimited Domestic Messaging 22, Data Used Unlimited Dist 5G iPhone w/VVM 1,258,</t>
-  </si>
-  <si>
-    <t>Talk Used Company fees &amp; surcharges Daytime minutes (unlimited) 1,729, Talk Used $1.34 Night &amp; Weekend minutes 52, Text Used Unlimited Domestic Messaging 519, Data Used Unlimited Dist 5G iPhone w/VVM 2,021,</t>
+    <t>Talk Used Company fees &amp; surcharges Daytime minutes (unlimited) 872, Talk Used $2.95 Night &amp; Weekend minutes 2, Text Used Government fees &amp; taxes Unlimited Domestic Messaging 77,</t>
+  </si>
+  <si>
+    <t>Talk Used $1.34 Daytime minutes (unlimited) 1,062, Talk Used $0.02 Night &amp; Weekend minutes 86, Text Used Government fees &amp; taxes Unlimited Domestic Messaging 19, Data Used Unlimited Dist 5G iPhone w/VVM 1,135,</t>
+  </si>
+  <si>
+    <t>Talk Used Company fees &amp; surcharges Daytime minutes (unlimited) 1,489, Talk Used $1.34 Night &amp; Weekend minutes 181, Text Used Unlimited Domestic Messaging 417, Data Used Unlimited Dist 5G iPhone w/VVM 5,390,</t>
   </si>
   <si>
     <t>50.84</t>
@@ -434,6 +437,9 @@
   </si>
   <si>
     <t>DISCOUNT FOR SMARTPHONE ACCESS CHARGE</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL DAY PASS FOR BUSINESS</t>
   </si>
   <si>
     <t>COUNTY SALES TAX - TELECOM</t>
@@ -999,7 +1005,7 @@
         <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1019,7 +1025,7 @@
         <v>82</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1039,7 +1045,7 @@
         <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1059,7 +1065,7 @@
         <v>84</v>
       </c>
       <c r="H5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1079,7 +1085,7 @@
         <v>85</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1099,7 +1105,7 @@
         <v>86</v>
       </c>
       <c r="H7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1119,7 +1125,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1139,7 +1145,7 @@
         <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1159,7 +1165,7 @@
         <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1179,7 +1185,7 @@
         <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1199,7 +1205,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1219,7 +1225,7 @@
         <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1239,7 +1245,7 @@
         <v>93</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1259,7 +1265,7 @@
         <v>94</v>
       </c>
       <c r="H15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1279,7 +1285,7 @@
         <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1299,7 +1305,7 @@
         <v>96</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1319,7 +1325,7 @@
         <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1336,10 +1342,10 @@
         <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1356,10 +1362,10 @@
         <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1376,7 +1382,7 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1393,10 +1399,10 @@
         <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1413,10 +1419,10 @@
         <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1481,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1498,13 +1504,13 @@
         <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1518,10 +1524,10 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2">
         <v>0.2</v>
@@ -1538,10 +1544,10 @@
         <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G3">
         <v>0.14</v>
@@ -1558,10 +1564,10 @@
         <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G4">
         <v>0.06</v>
@@ -1578,10 +1584,10 @@
         <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G5">
         <v>0.03</v>
@@ -1598,10 +1604,10 @@
         <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G6">
         <v>0.31</v>
@@ -1618,10 +1624,10 @@
         <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G7">
         <v>0.26</v>
@@ -1638,10 +1644,10 @@
         <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G8">
         <v>1.5</v>
@@ -1658,10 +1664,10 @@
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G9">
         <v>25.84</v>
@@ -1678,10 +1684,10 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G10">
         <v>25</v>
@@ -1698,10 +1704,10 @@
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1718,10 +1724,10 @@
         <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G12">
         <v>0.2</v>
@@ -1738,10 +1744,10 @@
         <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G13">
         <v>0.16</v>
@@ -1758,10 +1764,10 @@
         <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G14">
         <v>0.13</v>
@@ -1778,10 +1784,10 @@
         <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15">
         <v>0.02</v>
@@ -1798,10 +1804,10 @@
         <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16">
         <v>0.37</v>
@@ -1818,10 +1824,10 @@
         <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G17">
         <v>0.26</v>
@@ -1838,10 +1844,10 @@
         <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G18">
         <v>1.5</v>
@@ -1858,10 +1864,10 @@
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G19">
         <v>40</v>
@@ -1878,10 +1884,10 @@
         <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1898,10 +1904,10 @@
         <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21">
         <v>0.31</v>
@@ -1918,10 +1924,10 @@
         <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22">
         <v>0.02</v>
@@ -1938,10 +1944,10 @@
         <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G23">
         <v>0.26</v>
@@ -1958,10 +1964,10 @@
         <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G24">
         <v>1.5</v>
@@ -1978,10 +1984,10 @@
         <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G25">
         <v>1.5</v>
@@ -1998,10 +2004,10 @@
         <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G26">
         <v>0.37</v>
@@ -2018,10 +2024,10 @@
         <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G27">
         <v>20.28</v>
@@ -2038,10 +2044,10 @@
         <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G28">
         <v>40</v>
@@ -2058,10 +2064,10 @@
         <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2078,10 +2084,10 @@
         <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30">
         <v>-14.29</v>
@@ -2098,10 +2104,10 @@
         <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -2118,10 +2124,10 @@
         <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G32">
         <v>9.73</v>
@@ -2138,10 +2144,10 @@
         <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G33">
         <v>0.44</v>
@@ -2158,10 +2164,10 @@
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G34">
         <v>0.02</v>
@@ -2178,10 +2184,10 @@
         <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G35">
         <v>0.26</v>
@@ -2198,10 +2204,10 @@
         <v>61</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G36">
         <v>1.5</v>
@@ -2218,10 +2224,10 @@
         <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G37">
         <v>1.5</v>
@@ -2238,10 +2244,10 @@
         <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G38">
         <v>0.54</v>
@@ -2258,10 +2264,10 @@
         <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G39">
         <v>65</v>
@@ -2278,10 +2284,10 @@
         <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -2298,10 +2304,10 @@
         <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -2318,10 +2324,10 @@
         <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G42">
         <v>0.2</v>
@@ -2338,10 +2344,10 @@
         <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G43">
         <v>0.16</v>
@@ -2358,10 +2364,10 @@
         <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G44">
         <v>0.13</v>
@@ -2378,10 +2384,10 @@
         <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G45">
         <v>0.02</v>
@@ -2398,10 +2404,10 @@
         <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G46">
         <v>0.37</v>
@@ -2418,10 +2424,10 @@
         <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G47">
         <v>0.26</v>
@@ -2438,10 +2444,10 @@
         <v>62</v>
       </c>
       <c r="E48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G48">
         <v>1.5</v>
@@ -2458,10 +2464,10 @@
         <v>62</v>
       </c>
       <c r="E49" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G49">
         <v>40</v>
@@ -2478,10 +2484,10 @@
         <v>62</v>
       </c>
       <c r="E50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2498,10 +2504,10 @@
         <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F51" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G51">
         <v>0.2</v>
@@ -2518,10 +2524,10 @@
         <v>63</v>
       </c>
       <c r="E52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F52" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G52">
         <v>0.19</v>
@@ -2538,10 +2544,10 @@
         <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G53">
         <v>0.15</v>
@@ -2558,10 +2564,10 @@
         <v>63</v>
       </c>
       <c r="E54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G54">
         <v>0.02</v>
@@ -2578,10 +2584,10 @@
         <v>63</v>
       </c>
       <c r="E55" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G55">
         <v>0.46</v>
@@ -2598,10 +2604,10 @@
         <v>63</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G56">
         <v>0.26</v>
@@ -2618,10 +2624,10 @@
         <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G57">
         <v>1.5</v>
@@ -2638,10 +2644,10 @@
         <v>63</v>
       </c>
       <c r="E58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G58">
         <v>65</v>
@@ -2658,10 +2664,10 @@
         <v>63</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2678,13 +2684,13 @@
         <v>64</v>
       </c>
       <c r="E60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G60">
-        <v>0.35</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2698,10 +2704,10 @@
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G61">
         <v>0.26</v>
@@ -2718,10 +2724,10 @@
         <v>64</v>
       </c>
       <c r="E62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G62">
         <v>1.5</v>
@@ -2738,10 +2744,10 @@
         <v>64</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G63">
         <v>0.4</v>
@@ -2758,13 +2764,13 @@
         <v>64</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G64">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2778,13 +2784,13 @@
         <v>64</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G65">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2798,10 +2804,10 @@
         <v>64</v>
       </c>
       <c r="E66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G66">
         <v>60</v>
@@ -2818,10 +2824,10 @@
         <v>64</v>
       </c>
       <c r="E67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2838,10 +2844,10 @@
         <v>64</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G68">
         <v>-25</v>
@@ -2858,10 +2864,10 @@
         <v>64</v>
       </c>
       <c r="E69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -2872,19 +2878,19 @@
         <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E70" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F70" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="G70">
-        <v>0.35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2898,13 +2904,13 @@
         <v>65</v>
       </c>
       <c r="E71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F71" t="s">
         <v>121</v>
       </c>
       <c r="G71">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2918,13 +2924,13 @@
         <v>65</v>
       </c>
       <c r="E72" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
         <v>122</v>
       </c>
       <c r="G72">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2938,13 +2944,13 @@
         <v>65</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F73" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G73">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2958,13 +2964,13 @@
         <v>65</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F74" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="G74">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2978,13 +2984,13 @@
         <v>65</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F75" t="s">
         <v>135</v>
       </c>
       <c r="G75">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2998,13 +3004,13 @@
         <v>65</v>
       </c>
       <c r="E76" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F76" t="s">
         <v>136</v>
       </c>
       <c r="G76">
-        <v>60</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3018,13 +3024,13 @@
         <v>65</v>
       </c>
       <c r="E77" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
         <v>137</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3038,13 +3044,13 @@
         <v>65</v>
       </c>
       <c r="E78" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
         <v>138</v>
       </c>
       <c r="G78">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3058,13 +3064,13 @@
         <v>65</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3072,19 +3078,19 @@
         <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G80">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3098,13 +3104,13 @@
         <v>66</v>
       </c>
       <c r="E81" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F81" t="s">
         <v>117</v>
       </c>
       <c r="G81">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3118,13 +3124,13 @@
         <v>66</v>
       </c>
       <c r="E82" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F82" t="s">
         <v>118</v>
       </c>
       <c r="G82">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3138,13 +3144,13 @@
         <v>66</v>
       </c>
       <c r="E83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F83" t="s">
         <v>119</v>
       </c>
       <c r="G83">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3158,13 +3164,13 @@
         <v>66</v>
       </c>
       <c r="E84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F84" t="s">
         <v>120</v>
       </c>
       <c r="G84">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3178,13 +3184,13 @@
         <v>66</v>
       </c>
       <c r="E85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F85" t="s">
         <v>121</v>
       </c>
       <c r="G85">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3198,13 +3204,13 @@
         <v>66</v>
       </c>
       <c r="E86" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F86" t="s">
         <v>122</v>
       </c>
       <c r="G86">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3221,10 +3227,10 @@
         <v>113</v>
       </c>
       <c r="F87" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G87">
-        <v>60</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3238,13 +3244,13 @@
         <v>66</v>
       </c>
       <c r="E88" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>137</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3258,10 +3264,10 @@
         <v>66</v>
       </c>
       <c r="E89" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -3272,19 +3278,19 @@
         <v>19</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G90">
-        <v>0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3298,13 +3304,13 @@
         <v>67</v>
       </c>
       <c r="E91" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F91" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G91">
-        <v>0.02</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3318,13 +3324,13 @@
         <v>67</v>
       </c>
       <c r="E92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F92" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G92">
-        <v>0.26</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3338,13 +3344,13 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F93" t="s">
         <v>122</v>
       </c>
       <c r="G93">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3358,10 +3364,10 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F94" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G94">
         <v>1.5</v>
@@ -3378,13 +3384,13 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F95" t="s">
         <v>129</v>
       </c>
       <c r="G95">
-        <v>0.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3398,13 +3404,13 @@
         <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F96" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G96">
-        <v>60</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3418,13 +3424,13 @@
         <v>67</v>
       </c>
       <c r="E97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
         <v>137</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3438,10 +3444,10 @@
         <v>67</v>
       </c>
       <c r="E98" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -3452,19 +3458,19 @@
         <v>19</v>
       </c>
       <c r="B99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G99">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3478,13 +3484,13 @@
         <v>68</v>
       </c>
       <c r="E100" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F100" t="s">
         <v>117</v>
       </c>
       <c r="G100">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3498,13 +3504,13 @@
         <v>68</v>
       </c>
       <c r="E101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F101" t="s">
         <v>118</v>
       </c>
       <c r="G101">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3518,13 +3524,13 @@
         <v>68</v>
       </c>
       <c r="E102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F102" t="s">
         <v>119</v>
       </c>
       <c r="G102">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3538,13 +3544,13 @@
         <v>68</v>
       </c>
       <c r="E103" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F103" t="s">
         <v>120</v>
       </c>
       <c r="G103">
-        <v>0.35</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3558,13 +3564,13 @@
         <v>68</v>
       </c>
       <c r="E104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F104" t="s">
         <v>121</v>
       </c>
       <c r="G104">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3578,13 +3584,13 @@
         <v>68</v>
       </c>
       <c r="E105" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F105" t="s">
         <v>122</v>
       </c>
       <c r="G105">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3601,10 +3607,10 @@
         <v>113</v>
       </c>
       <c r="F106" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G106">
-        <v>60</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3618,13 +3624,13 @@
         <v>68</v>
       </c>
       <c r="E107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F107" t="s">
         <v>137</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3638,13 +3644,13 @@
         <v>68</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F108" t="s">
         <v>138</v>
       </c>
       <c r="G108">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3658,13 +3664,13 @@
         <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F109" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3672,19 +3678,19 @@
         <v>19</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C110" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E110" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F110" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G110">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3698,13 +3704,13 @@
         <v>69</v>
       </c>
       <c r="E111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F111" t="s">
         <v>117</v>
       </c>
       <c r="G111">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3718,13 +3724,13 @@
         <v>69</v>
       </c>
       <c r="E112" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F112" t="s">
         <v>118</v>
       </c>
       <c r="G112">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3738,13 +3744,13 @@
         <v>69</v>
       </c>
       <c r="E113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F113" t="s">
         <v>119</v>
       </c>
       <c r="G113">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3758,13 +3764,13 @@
         <v>69</v>
       </c>
       <c r="E114" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F114" t="s">
         <v>120</v>
       </c>
       <c r="G114">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3778,13 +3784,13 @@
         <v>69</v>
       </c>
       <c r="E115" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F115" t="s">
         <v>121</v>
       </c>
       <c r="G115">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3798,13 +3804,13 @@
         <v>69</v>
       </c>
       <c r="E116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F116" t="s">
         <v>122</v>
       </c>
       <c r="G116">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3821,10 +3827,10 @@
         <v>113</v>
       </c>
       <c r="F117" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G117">
-        <v>60</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3838,13 +3844,13 @@
         <v>69</v>
       </c>
       <c r="E118" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F118" t="s">
         <v>137</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3858,10 +3864,10 @@
         <v>69</v>
       </c>
       <c r="E119" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F119" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -3872,19 +3878,19 @@
         <v>19</v>
       </c>
       <c r="B120" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E120" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F120" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G120">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3898,13 +3904,13 @@
         <v>70</v>
       </c>
       <c r="E121" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F121" t="s">
         <v>121</v>
       </c>
       <c r="G121">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3918,13 +3924,13 @@
         <v>70</v>
       </c>
       <c r="E122" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F122" t="s">
         <v>122</v>
       </c>
       <c r="G122">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3938,13 +3944,13 @@
         <v>70</v>
       </c>
       <c r="E123" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F123" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G123">
-        <v>0.04</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3958,13 +3964,13 @@
         <v>70</v>
       </c>
       <c r="E124" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F124" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3978,13 +3984,13 @@
         <v>70</v>
       </c>
       <c r="E125" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F125" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G125">
-        <v>0.13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3998,13 +4004,13 @@
         <v>70</v>
       </c>
       <c r="E126" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F126" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G126">
-        <v>60</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4018,13 +4024,13 @@
         <v>70</v>
       </c>
       <c r="E127" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F127" t="s">
         <v>137</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4038,13 +4044,13 @@
         <v>70</v>
       </c>
       <c r="E128" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F128" t="s">
         <v>138</v>
       </c>
       <c r="G128">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4058,13 +4064,13 @@
         <v>70</v>
       </c>
       <c r="E129" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F129" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4078,10 +4084,10 @@
         <v>70</v>
       </c>
       <c r="E130" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F130" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -4092,19 +4098,19 @@
         <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C131" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E131" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F131" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G131">
-        <v>0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4118,13 +4124,13 @@
         <v>71</v>
       </c>
       <c r="E132" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F132" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="G132">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4138,13 +4144,13 @@
         <v>71</v>
       </c>
       <c r="E133" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F133" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G133">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4158,13 +4164,13 @@
         <v>71</v>
       </c>
       <c r="E134" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F134" t="s">
         <v>122</v>
       </c>
       <c r="G134">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4178,13 +4184,13 @@
         <v>71</v>
       </c>
       <c r="E135" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F135" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="G135">
-        <v>0.13</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4198,13 +4204,13 @@
         <v>71</v>
       </c>
       <c r="E136" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F136" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G136">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4218,13 +4224,13 @@
         <v>71</v>
       </c>
       <c r="E137" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F137" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4238,13 +4244,13 @@
         <v>71</v>
       </c>
       <c r="E138" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F138" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G138">
-        <v>0.19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4258,13 +4264,13 @@
         <v>71</v>
       </c>
       <c r="E139" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F139" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G139">
-        <v>60</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4278,13 +4284,13 @@
         <v>71</v>
       </c>
       <c r="E140" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F140" t="s">
         <v>137</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4298,10 +4304,10 @@
         <v>71</v>
       </c>
       <c r="E141" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F141" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -4312,19 +4318,19 @@
         <v>19</v>
       </c>
       <c r="B142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C142" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E142" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F142" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G142">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4338,13 +4344,13 @@
         <v>72</v>
       </c>
       <c r="E143" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F143" t="s">
         <v>117</v>
       </c>
       <c r="G143">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4358,13 +4364,13 @@
         <v>72</v>
       </c>
       <c r="E144" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F144" t="s">
         <v>118</v>
       </c>
       <c r="G144">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4378,13 +4384,13 @@
         <v>72</v>
       </c>
       <c r="E145" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F145" t="s">
         <v>119</v>
       </c>
       <c r="G145">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4398,13 +4404,13 @@
         <v>72</v>
       </c>
       <c r="E146" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F146" t="s">
         <v>120</v>
       </c>
       <c r="G146">
-        <v>0.35</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4418,13 +4424,13 @@
         <v>72</v>
       </c>
       <c r="E147" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F147" t="s">
         <v>121</v>
       </c>
       <c r="G147">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4438,13 +4444,13 @@
         <v>72</v>
       </c>
       <c r="E148" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F148" t="s">
         <v>122</v>
       </c>
       <c r="G148">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4461,10 +4467,10 @@
         <v>113</v>
       </c>
       <c r="F149" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="G149">
-        <v>60</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4478,13 +4484,13 @@
         <v>72</v>
       </c>
       <c r="E150" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F150" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4498,10 +4504,10 @@
         <v>72</v>
       </c>
       <c r="E151" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F151" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -4518,13 +4524,13 @@
         <v>72</v>
       </c>
       <c r="E152" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F152" t="s">
         <v>138</v>
       </c>
       <c r="G152">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4538,13 +4544,13 @@
         <v>72</v>
       </c>
       <c r="E153" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F153" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4552,19 +4558,19 @@
         <v>19</v>
       </c>
       <c r="B154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C154" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E154" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F154" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G154">
-        <v>0.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4578,13 +4584,13 @@
         <v>73</v>
       </c>
       <c r="E155" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F155" t="s">
         <v>122</v>
       </c>
       <c r="G155">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4598,13 +4604,13 @@
         <v>73</v>
       </c>
       <c r="E156" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F156" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="G156">
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4621,10 +4627,10 @@
         <v>113</v>
       </c>
       <c r="F157" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G157">
-        <v>40</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4632,19 +4638,19 @@
         <v>19</v>
       </c>
       <c r="B158" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C158" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E158" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F158" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="G158">
-        <v>0.26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4658,13 +4664,13 @@
         <v>74</v>
       </c>
       <c r="E159" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F159" t="s">
         <v>122</v>
       </c>
       <c r="G159">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4681,10 +4687,10 @@
         <v>113</v>
       </c>
       <c r="F160" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G160">
-        <v>40</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4692,19 +4698,19 @@
         <v>19</v>
       </c>
       <c r="B161" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C161" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E161" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F161" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="G161">
-        <v>0.26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4718,13 +4724,13 @@
         <v>75</v>
       </c>
       <c r="E162" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F162" t="s">
         <v>122</v>
       </c>
       <c r="G162">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4741,10 +4747,10 @@
         <v>113</v>
       </c>
       <c r="F163" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G163">
-        <v>40</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4752,19 +4758,19 @@
         <v>19</v>
       </c>
       <c r="B164" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C164" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E164" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F164" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G164">
-        <v>2.95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4778,13 +4784,13 @@
         <v>76</v>
       </c>
       <c r="E165" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F165" t="s">
         <v>121</v>
       </c>
       <c r="G165">
-        <v>0.26</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4798,13 +4804,13 @@
         <v>76</v>
       </c>
       <c r="E166" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F166" t="s">
         <v>122</v>
       </c>
       <c r="G166">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4818,13 +4824,13 @@
         <v>76</v>
       </c>
       <c r="E167" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F167" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G167">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4838,13 +4844,13 @@
         <v>76</v>
       </c>
       <c r="E168" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F168" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="G168">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4858,13 +4864,13 @@
         <v>76</v>
       </c>
       <c r="E169" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F169" t="s">
         <v>135</v>
       </c>
       <c r="G169">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4878,13 +4884,13 @@
         <v>76</v>
       </c>
       <c r="E170" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F170" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G170">
-        <v>80</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4898,13 +4904,13 @@
         <v>76</v>
       </c>
       <c r="E171" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F171" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G171">
-        <v>-8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4912,19 +4918,19 @@
         <v>19</v>
       </c>
       <c r="B172" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C172" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E172" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F172" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="G172">
-        <v>1.34</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4938,13 +4944,13 @@
         <v>77</v>
       </c>
       <c r="E173" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F173" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G173">
-        <v>0.02</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4958,13 +4964,13 @@
         <v>77</v>
       </c>
       <c r="E174" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F174" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G174">
-        <v>0.26</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4978,13 +4984,13 @@
         <v>77</v>
       </c>
       <c r="E175" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F175" t="s">
         <v>122</v>
       </c>
       <c r="G175">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4998,10 +5004,10 @@
         <v>77</v>
       </c>
       <c r="E176" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F176" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G176">
         <v>1.5</v>
@@ -5018,13 +5024,13 @@
         <v>77</v>
       </c>
       <c r="E177" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F177" t="s">
         <v>129</v>
       </c>
       <c r="G177">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5038,13 +5044,13 @@
         <v>77</v>
       </c>
       <c r="E178" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F178" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5058,13 +5064,13 @@
         <v>77</v>
       </c>
       <c r="E179" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F179" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G179">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5072,19 +5078,19 @@
         <v>19</v>
       </c>
       <c r="B180" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C180" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E180" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F180" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="G180">
-        <v>1.34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5098,13 +5104,13 @@
         <v>78</v>
       </c>
       <c r="E181" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F181" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G181">
-        <v>0.02</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5118,13 +5124,13 @@
         <v>78</v>
       </c>
       <c r="E182" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F182" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G182">
-        <v>0.26</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5138,13 +5144,13 @@
         <v>78</v>
       </c>
       <c r="E183" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F183" t="s">
         <v>122</v>
       </c>
       <c r="G183">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5158,10 +5164,10 @@
         <v>78</v>
       </c>
       <c r="E184" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F184" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G184">
         <v>1.5</v>
@@ -5178,13 +5184,13 @@
         <v>78</v>
       </c>
       <c r="E185" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F185" t="s">
         <v>129</v>
       </c>
       <c r="G185">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5198,13 +5204,13 @@
         <v>78</v>
       </c>
       <c r="E186" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F186" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="G186">
-        <v>85</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5212,19 +5218,19 @@
         <v>19</v>
       </c>
       <c r="B187" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E187" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F187" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="G187">
-        <v>1.34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5238,13 +5244,13 @@
         <v>79</v>
       </c>
       <c r="E188" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F188" t="s">
         <v>121</v>
       </c>
       <c r="G188">
-        <v>0.26</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5258,13 +5264,13 @@
         <v>79</v>
       </c>
       <c r="E189" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F189" t="s">
         <v>122</v>
       </c>
       <c r="G189">
-        <v>1.5</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5278,13 +5284,13 @@
         <v>79</v>
       </c>
       <c r="E190" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F190" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="G190">
-        <v>0.85</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5298,13 +5304,13 @@
         <v>79</v>
       </c>
       <c r="E191" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F191" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G191">
-        <v>0.32</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5318,13 +5324,13 @@
         <v>79</v>
       </c>
       <c r="E192" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F192" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G192">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5338,13 +5344,13 @@
         <v>79</v>
       </c>
       <c r="E193" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F193" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G193">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5358,13 +5364,13 @@
         <v>79</v>
       </c>
       <c r="E194" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F194" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G194">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5378,13 +5384,13 @@
         <v>79</v>
       </c>
       <c r="E195" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F195" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G195">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5398,13 +5404,13 @@
         <v>79</v>
       </c>
       <c r="E196" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F196" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5418,12 +5424,32 @@
         <v>79</v>
       </c>
       <c r="E197" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F197" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" t="s">
+        <v>52</v>
+      </c>
+      <c r="C198" t="s">
+        <v>79</v>
+      </c>
+      <c r="E198" t="s">
+        <v>114</v>
+      </c>
+      <c r="F198" t="s">
+        <v>154</v>
+      </c>
+      <c r="G198">
         <v>85</v>
       </c>
     </row>
@@ -5451,10 +5477,10 @@
         <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5471,7 +5497,7 @@
         <v>53.34</v>
       </c>
       <c r="F2">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5488,7 +5514,7 @@
         <v>42.64</v>
       </c>
       <c r="F3">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5505,7 +5531,7 @@
         <v>64.68000000000001</v>
       </c>
       <c r="F4">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5522,7 +5548,7 @@
         <v>74.26000000000001</v>
       </c>
       <c r="F5">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5539,7 +5565,7 @@
         <v>42.64</v>
       </c>
       <c r="F6">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5556,7 +5582,7 @@
         <v>67.78</v>
       </c>
       <c r="F7">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5570,10 +5596,10 @@
         <v>64</v>
       </c>
       <c r="E8">
-        <v>37.81</v>
+        <v>62.67</v>
       </c>
       <c r="F8">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5590,7 +5616,7 @@
         <v>37.81</v>
       </c>
       <c r="F9">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5607,7 +5633,7 @@
         <v>62.75</v>
       </c>
       <c r="F10">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5624,7 +5650,7 @@
         <v>64.25999999999999</v>
       </c>
       <c r="F11">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5641,7 +5667,7 @@
         <v>37.6</v>
       </c>
       <c r="F12">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5658,7 +5684,7 @@
         <v>62.75</v>
       </c>
       <c r="F13">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5675,7 +5701,7 @@
         <v>38.28</v>
       </c>
       <c r="F14">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5692,7 +5718,7 @@
         <v>63.98</v>
       </c>
       <c r="F15">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -5709,7 +5735,7 @@
         <v>37.6</v>
       </c>
       <c r="F16">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5726,7 +5752,7 @@
         <v>41.91</v>
       </c>
       <c r="F17">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5743,7 +5769,7 @@
         <v>41.76</v>
       </c>
       <c r="F18">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5760,7 +5786,7 @@
         <v>41.76</v>
       </c>
       <c r="F19">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5777,7 +5803,7 @@
         <v>81.34</v>
       </c>
       <c r="F20">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5794,7 +5820,7 @@
         <v>91.41</v>
       </c>
       <c r="F21">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5811,7 +5837,7 @@
         <v>91.41</v>
       </c>
       <c r="F22">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5828,7 +5854,7 @@
         <v>90.95999999999999</v>
       </c>
       <c r="F23">
-        <v>1268.73</v>
+        <v>1293.59</v>
       </c>
     </row>
   </sheetData>
